--- a/time-const-train-loss_b-100_d-10000_tc-20_tw-80.xlsx
+++ b/time-const-train-loss_b-100_d-10000_tc-20_tw-80.xlsx
@@ -383,13 +383,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1588986963033676</v>
+        <v>0.1312287002801895</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0003956028958782554</v>
+        <v>0.002880334388464689</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004748226143419743</v>
+        <v>0.8774020075798035</v>
       </c>
     </row>
     <row r="3">
@@ -397,13 +397,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1638791710138321</v>
+        <v>0.1466213464736938</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0003955386928282678</v>
+        <v>0.00424153171479702</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005533547606319189</v>
+        <v>0.8393619060516357</v>
       </c>
     </row>
     <row r="4">
@@ -411,13 +411,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1653679460287094</v>
+        <v>0.1480099260807037</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0003954834537580609</v>
+        <v>0.003774793120101094</v>
       </c>
       <c r="D4" t="n">
-        <v>0.007683003321290016</v>
+        <v>0.8495725393295288</v>
       </c>
     </row>
     <row r="5">
@@ -425,13 +425,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1588034480810165</v>
+        <v>0.1414844542741776</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0003954379935748875</v>
+        <v>0.00399590190500021</v>
       </c>
       <c r="D5" t="n">
-        <v>0.007692653220146894</v>
+        <v>0.8770090937614441</v>
       </c>
     </row>
     <row r="6">
@@ -439,13 +439,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1624036878347397</v>
+        <v>0.1452678292989731</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003953736741095781</v>
+        <v>0.003153030527755618</v>
       </c>
       <c r="D6" t="n">
-        <v>0.006713126786053181</v>
+        <v>0.8229144811630249</v>
       </c>
     </row>
     <row r="7">
@@ -453,13 +453,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.162348285317421</v>
+        <v>0.14388507604599</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0003953087725676596</v>
+        <v>0.00404725968837738</v>
       </c>
       <c r="D7" t="n">
-        <v>0.006077294703572989</v>
+        <v>0.7943452000617981</v>
       </c>
     </row>
     <row r="8">
@@ -467,13 +467,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1592880338430405</v>
+        <v>0.1417623460292816</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0003952339757233858</v>
+        <v>0.00302360113710165</v>
       </c>
       <c r="D8" t="n">
-        <v>0.005309163127094507</v>
+        <v>0.9093946218490601</v>
       </c>
     </row>
     <row r="9">
@@ -481,13 +481,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1632827669382095</v>
+        <v>0.1536291539669037</v>
       </c>
       <c r="C9" t="n">
-        <v>0.000395163195207715</v>
+        <v>0.003507961053401232</v>
       </c>
       <c r="D9" t="n">
-        <v>0.006030810996890068</v>
+        <v>0.893156111240387</v>
       </c>
     </row>
     <row r="10">
@@ -495,13 +495,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1650544404983521</v>
+        <v>0.1472584456205368</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0003951126127503812</v>
+        <v>0.003335300600156188</v>
       </c>
       <c r="D10" t="n">
-        <v>0.006881780456751585</v>
+        <v>0.8275747895240784</v>
       </c>
     </row>
     <row r="11">
@@ -509,13 +509,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1634556800127029</v>
+        <v>0.1393419057130814</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0003950660466216505</v>
+        <v>0.003992788027971983</v>
       </c>
       <c r="D11" t="n">
-        <v>0.006600076798349619</v>
+        <v>0.8685967326164246</v>
       </c>
     </row>
     <row r="12">
@@ -523,13 +523,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.1536464840173721</v>
+        <v>0.1478514969348907</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0003949930251110345</v>
+        <v>0.003553625894710422</v>
       </c>
       <c r="D12" t="n">
-        <v>0.004686844535171986</v>
+        <v>0.8475222587585449</v>
       </c>
     </row>
     <row r="13">
@@ -537,13 +537,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1607348769903183</v>
+        <v>0.146274596452713</v>
       </c>
       <c r="C13" t="n">
-        <v>0.000394908245652914</v>
+        <v>0.00344420038163662</v>
       </c>
       <c r="D13" t="n">
-        <v>0.004533046390861273</v>
+        <v>0.8265610933303833</v>
       </c>
     </row>
     <row r="14">
@@ -551,13 +551,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1729761064052582</v>
+        <v>0.1468953341245651</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0003948613593820482</v>
+        <v>0.004765285179018974</v>
       </c>
       <c r="D14" t="n">
-        <v>0.005688989534974098</v>
+        <v>0.8423764109611511</v>
       </c>
     </row>
     <row r="15">
@@ -565,13 +565,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.1733066588640213</v>
+        <v>0.1466240584850311</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0003948653466068208</v>
+        <v>0.003297879360616207</v>
       </c>
       <c r="D15" t="n">
-        <v>0.006018404383212328</v>
+        <v>0.878174364566803</v>
       </c>
     </row>
     <row r="16">
@@ -579,13 +579,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1648828685283661</v>
+        <v>0.1366045922040939</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0003948654048144817</v>
+        <v>0.003323232056573033</v>
       </c>
       <c r="D16" t="n">
-        <v>0.005252690520137548</v>
+        <v>0.8322778940200806</v>
       </c>
     </row>
     <row r="17">
@@ -593,13 +593,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.1649532169103622</v>
+        <v>0.1429645270109177</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0003948089433833957</v>
+        <v>0.003348507219925523</v>
       </c>
       <c r="D17" t="n">
-        <v>0.005183854606002569</v>
+        <v>0.8271100521087646</v>
       </c>
     </row>
     <row r="18">
@@ -607,13 +607,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1625961810350418</v>
+        <v>0.153418630361557</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0003947544901166111</v>
+        <v>0.004574810620397329</v>
       </c>
       <c r="D18" t="n">
-        <v>0.005509974434971809</v>
+        <v>0.7723270654678345</v>
       </c>
     </row>
     <row r="19">
@@ -621,13 +621,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.164195790886879</v>
+        <v>0.1436084657907486</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0003947106597479433</v>
+        <v>0.003974760882556438</v>
       </c>
       <c r="D19" t="n">
-        <v>0.004374844487756491</v>
+        <v>0.8680614829063416</v>
       </c>
     </row>
     <row r="20">
@@ -635,13 +635,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.1649205833673477</v>
+        <v>0.1427278965711594</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0003946579527109861</v>
+        <v>0.00403046328574419</v>
       </c>
       <c r="D20" t="n">
-        <v>0.005398653447628021</v>
+        <v>0.8586968779563904</v>
       </c>
     </row>
     <row r="21">
@@ -649,13 +649,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.1677933931350708</v>
+        <v>0.1368945837020874</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0003946290235035121</v>
+        <v>0.004287448246032</v>
       </c>
       <c r="D21" t="n">
-        <v>0.006051596719771624</v>
+        <v>0.8640387058258057</v>
       </c>
     </row>
     <row r="22">
@@ -663,13 +663,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>0.1669673174619675</v>
+        <v>0.1465337723493576</v>
       </c>
       <c r="C22" t="n">
-        <v>0.000394613656681031</v>
+        <v>0.003417706815525889</v>
       </c>
       <c r="D22" t="n">
-        <v>0.006756002083420753</v>
+        <v>0.8669424653053284</v>
       </c>
     </row>
     <row r="23">
@@ -677,13 +677,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>0.163640171289444</v>
+        <v>0.1479218155145645</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0003945853095501661</v>
+        <v>0.004338828381150961</v>
       </c>
       <c r="D23" t="n">
-        <v>0.007568428292870522</v>
+        <v>0.853061854839325</v>
       </c>
     </row>
     <row r="24">
@@ -691,13 +691,13 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>0.1721197962760925</v>
+        <v>0.1314908415079117</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0003945417120121419</v>
+        <v>0.00346099934540689</v>
       </c>
       <c r="D24" t="n">
-        <v>0.004842441063374281</v>
+        <v>0.830644965171814</v>
       </c>
     </row>
     <row r="25">
@@ -705,13 +705,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>0.1638653725385666</v>
+        <v>0.1434858441352844</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0003945204662159085</v>
+        <v>0.00554330600425601</v>
       </c>
       <c r="D25" t="n">
-        <v>0.005783011671155691</v>
+        <v>0.8229943513870239</v>
       </c>
     </row>
     <row r="26">
@@ -719,13 +719,13 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>0.160845622420311</v>
+        <v>0.1478056609630585</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0003944584168493748</v>
+        <v>0.00453938078135252</v>
       </c>
       <c r="D26" t="n">
-        <v>0.006527979392558336</v>
+        <v>0.7960482835769653</v>
       </c>
     </row>
     <row r="27">
@@ -733,13 +733,13 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>0.1686206758022308</v>
+        <v>0.149592325091362</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0003943912161048502</v>
+        <v>0.004615149926394224</v>
       </c>
       <c r="D27" t="n">
-        <v>0.005606401246041059</v>
+        <v>0.790149450302124</v>
       </c>
     </row>
     <row r="28">
@@ -747,13 +747,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>0.1700950413942337</v>
+        <v>0.1394622325897217</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0003943519259337336</v>
+        <v>0.003548098960891366</v>
       </c>
       <c r="D28" t="n">
-        <v>0.005071395542472601</v>
+        <v>0.8261101245880127</v>
       </c>
     </row>
     <row r="29">
@@ -761,13 +761,13 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>0.1693626940250397</v>
+        <v>0.1383628696203232</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0003943081828765571</v>
+        <v>0.00473787821829319</v>
       </c>
       <c r="D29" t="n">
-        <v>0.005351949483156204</v>
+        <v>0.8169132471084595</v>
       </c>
     </row>
     <row r="30">
@@ -775,13 +775,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>0.1704747527837753</v>
+        <v>0.1376686245203018</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0003942865296266973</v>
+        <v>0.004113387782126665</v>
       </c>
       <c r="D30" t="n">
-        <v>0.006164265796542168</v>
+        <v>0.768821120262146</v>
       </c>
     </row>
     <row r="31">
@@ -789,13 +789,13 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>0.1630328148603439</v>
+        <v>0.1372792571783066</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0003942683106288314</v>
+        <v>0.002773393411189318</v>
       </c>
       <c r="D31" t="n">
-        <v>0.00533889327198267</v>
+        <v>0.8594385385513306</v>
       </c>
     </row>
     <row r="32">
@@ -803,13 +803,13 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>0.1653914898633957</v>
+        <v>0.1490741223096848</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0003942217445001006</v>
+        <v>0.00429763225838542</v>
       </c>
       <c r="D32" t="n">
-        <v>0.003656791057437658</v>
+        <v>0.7907074093818665</v>
       </c>
     </row>
     <row r="33">
@@ -817,13 +817,13 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>0.1592467576265335</v>
+        <v>0.1444254964590073</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0003941579780075699</v>
+        <v>0.004121088422834873</v>
       </c>
       <c r="D33" t="n">
-        <v>0.004753913730382919</v>
+        <v>0.8574315905570984</v>
       </c>
     </row>
     <row r="34">
@@ -831,13 +831,13 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>0.1551969349384308</v>
+        <v>0.1524404734373093</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0003940891765523702</v>
+        <v>0.004091303795576096</v>
       </c>
       <c r="D34" t="n">
-        <v>0.005916917230933905</v>
+        <v>0.8016266822814941</v>
       </c>
     </row>
     <row r="35">
@@ -845,13 +845,13 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>0.1624895036220551</v>
+        <v>0.1452511847019196</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0003940341412089765</v>
+        <v>0.003993549384176731</v>
       </c>
       <c r="D35" t="n">
-        <v>0.006004294380545616</v>
+        <v>0.8045885562896729</v>
       </c>
     </row>
     <row r="36">
@@ -859,13 +859,13 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>0.1573309600353241</v>
+        <v>0.14234659075737</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0003939833259209991</v>
+        <v>0.004115213640034199</v>
       </c>
       <c r="D36" t="n">
-        <v>0.005137939937412739</v>
+        <v>0.8321657776832581</v>
       </c>
     </row>
     <row r="37">
@@ -873,13 +873,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>0.1671268492937088</v>
+        <v>0.1381933987140656</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0003939236339647323</v>
+        <v>0.003081569215282798</v>
       </c>
       <c r="D37" t="n">
-        <v>0.004276503343135118</v>
+        <v>0.8857098817825317</v>
       </c>
     </row>
     <row r="38">
@@ -887,13 +887,13 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>0.1745284497737885</v>
+        <v>0.1470259130001068</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0003938820445910096</v>
+        <v>0.003848655615001917</v>
       </c>
       <c r="D38" t="n">
-        <v>0.004542278125882149</v>
+        <v>0.8085982799530029</v>
       </c>
     </row>
     <row r="39">
@@ -901,13 +901,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>0.1669456660747528</v>
+        <v>0.1428521871566772</v>
       </c>
       <c r="C39" t="n">
-        <v>0.000393866968806833</v>
+        <v>0.003402425674721599</v>
       </c>
       <c r="D39" t="n">
-        <v>0.005757677368819714</v>
+        <v>0.8128648996353149</v>
       </c>
     </row>
     <row r="40">
@@ -915,13 +915,13 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>0.1655677407979965</v>
+        <v>0.1437265574932098</v>
       </c>
       <c r="C40" t="n">
-        <v>0.00039382089744322</v>
+        <v>0.003124762326478958</v>
       </c>
       <c r="D40" t="n">
-        <v>0.005607907194644213</v>
+        <v>0.7804235219955444</v>
       </c>
     </row>
     <row r="41">
@@ -929,13 +929,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>0.1638301908969879</v>
+        <v>0.1523486375808716</v>
       </c>
       <c r="C41" t="n">
-        <v>0.00039377884240821</v>
+        <v>0.00340786948800087</v>
       </c>
       <c r="D41" t="n">
-        <v>0.005279903765767813</v>
+        <v>0.8103315830230713</v>
       </c>
     </row>
     <row r="42">
@@ -943,13 +943,13 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>0.165139839053154</v>
+        <v>0.1419199258089066</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0003937315486837178</v>
+        <v>0.004625675734132528</v>
       </c>
       <c r="D42" t="n">
-        <v>0.006459418218582869</v>
+        <v>0.7927009463310242</v>
       </c>
     </row>
     <row r="43">
@@ -957,13 +957,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>0.1594609320163727</v>
+        <v>0.1284789592027664</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0003936885914299637</v>
+        <v>0.005374297499656677</v>
       </c>
       <c r="D43" t="n">
-        <v>0.007642802782356739</v>
+        <v>0.8568012714385986</v>
       </c>
     </row>
     <row r="44">
@@ -971,13 +971,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>0.1667290776968002</v>
+        <v>0.1508828550577164</v>
       </c>
       <c r="C44" t="n">
-        <v>0.000393638270907104</v>
+        <v>0.003630512626841664</v>
       </c>
       <c r="D44" t="n">
-        <v>0.005538602359592915</v>
+        <v>0.8094196319580078</v>
       </c>
     </row>
     <row r="45">
@@ -985,13 +985,13 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>0.1584319770336151</v>
+        <v>0.1515528857707977</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0003935968270525336</v>
+        <v>0.003122348105534911</v>
       </c>
       <c r="D45" t="n">
-        <v>0.004259375855326653</v>
+        <v>0.7873324751853943</v>
       </c>
     </row>
     <row r="46">
@@ -999,13 +999,13 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>0.1641004085540771</v>
+        <v>0.1395833045244217</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0003935214481316507</v>
+        <v>0.003628092352300882</v>
       </c>
       <c r="D46" t="n">
-        <v>0.005712743382900953</v>
+        <v>0.8185434937477112</v>
       </c>
     </row>
     <row r="47">
@@ -1013,13 +1013,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>0.1683218330144882</v>
+        <v>0.1548901945352554</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0003934843116439879</v>
+        <v>0.004523634444922209</v>
       </c>
       <c r="D47" t="n">
-        <v>0.005373766645789146</v>
+        <v>0.7260622978210449</v>
       </c>
     </row>
     <row r="48">
@@ -1027,13 +1027,13 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>0.1747663617134094</v>
+        <v>0.1483861654996872</v>
       </c>
       <c r="C48" t="n">
-        <v>0.000393466092646122</v>
+        <v>0.005647961515933275</v>
       </c>
       <c r="D48" t="n">
-        <v>0.005042241886258125</v>
+        <v>0.7643997669219971</v>
       </c>
     </row>
     <row r="49">
@@ -1041,13 +1041,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>0.1721303910017014</v>
+        <v>0.1475455313920975</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0003934542182832956</v>
+        <v>0.003375079017132521</v>
       </c>
       <c r="D49" t="n">
-        <v>0.005590516142547131</v>
+        <v>0.8044504523277283</v>
       </c>
     </row>
     <row r="50">
@@ -1055,13 +1055,13 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>0.1763794720172882</v>
+        <v>0.137165367603302</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0003934379492420703</v>
+        <v>0.003522623563185334</v>
       </c>
       <c r="D50" t="n">
-        <v>0.005812146235257387</v>
+        <v>0.810117781162262</v>
       </c>
     </row>
     <row r="51">
@@ -1069,13 +1069,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>0.1609970033168793</v>
+        <v>0.1376391500234604</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0003934198175556958</v>
+        <v>0.003433904144912958</v>
       </c>
       <c r="D51" t="n">
-        <v>0.007496730424463749</v>
+        <v>0.7540739774703979</v>
       </c>
     </row>
     <row r="52">
@@ -1083,13 +1083,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>0.1648714691400528</v>
+        <v>0.1351286768913269</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0003933525294996798</v>
+        <v>0.003332057734951377</v>
       </c>
       <c r="D52" t="n">
-        <v>0.006285323295742273</v>
+        <v>0.8037262558937073</v>
       </c>
     </row>
     <row r="53">
@@ -1097,13 +1097,13 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>0.1690006405115128</v>
+        <v>0.1471662521362305</v>
       </c>
       <c r="C53" t="n">
-        <v>0.00039330730214715</v>
+        <v>0.0036411436740309</v>
       </c>
       <c r="D53" t="n">
-        <v>0.005422679707407951</v>
+        <v>0.8131119012832642</v>
       </c>
     </row>
     <row r="54">
@@ -1111,13 +1111,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>0.1639353483915329</v>
+        <v>0.136220395565033</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0003932695253752172</v>
+        <v>0.004094914998859167</v>
       </c>
       <c r="D54" t="n">
-        <v>0.006099972408264875</v>
+        <v>0.805090606212616</v>
       </c>
     </row>
     <row r="55">
@@ -1125,13 +1125,13 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>0.1735458523035049</v>
+        <v>0.1615153849124908</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0003932135296054184</v>
+        <v>0.003829304594546556</v>
       </c>
       <c r="D55" t="n">
-        <v>0.005031566135585308</v>
+        <v>0.7260468006134033</v>
       </c>
     </row>
     <row r="56">
@@ -1139,13 +1139,13 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>0.1711889803409576</v>
+        <v>0.144615426659584</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0003931957180611789</v>
+        <v>0.00402309512719512</v>
       </c>
       <c r="D56" t="n">
-        <v>0.006171077489852905</v>
+        <v>0.7970688939094543</v>
       </c>
     </row>
     <row r="57">
@@ -1153,13 +1153,13 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>0.1661364138126373</v>
+        <v>0.1401718705892563</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0003931898390874267</v>
+        <v>0.003291037632152438</v>
       </c>
       <c r="D57" t="n">
-        <v>0.004799690097570419</v>
+        <v>0.7704346179962158</v>
       </c>
     </row>
     <row r="58">
@@ -1167,13 +1167,13 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>0.1673777550458908</v>
+        <v>0.151029497385025</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0003931433311663568</v>
+        <v>0.006245633121579885</v>
       </c>
       <c r="D58" t="n">
-        <v>0.006034115795046091</v>
+        <v>0.8154703378677368</v>
       </c>
     </row>
     <row r="59">
@@ -1181,13 +1181,13 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>0.1598099619150162</v>
+        <v>0.1380409300327301</v>
       </c>
       <c r="C59" t="n">
-        <v>0.0003930957755073905</v>
+        <v>0.004787462763488293</v>
       </c>
       <c r="D59" t="n">
-        <v>0.006852076388895512</v>
+        <v>0.8137650489807129</v>
       </c>
     </row>
     <row r="60">
@@ -1195,13 +1195,13 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>0.1584005653858185</v>
+        <v>0.1552764624357224</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0003930365783162415</v>
+        <v>0.00598434079438448</v>
       </c>
       <c r="D60" t="n">
-        <v>0.005575686227530241</v>
+        <v>0.7277736663818359</v>
       </c>
     </row>
     <row r="61">
@@ -1209,13 +1209,13 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>0.1668077260255814</v>
+        <v>0.155068427324295</v>
       </c>
       <c r="C61" t="n">
-        <v>0.0003929712111130357</v>
+        <v>0.004400130826979876</v>
       </c>
       <c r="D61" t="n">
-        <v>0.006092994008213282</v>
+        <v>0.7507257461547852</v>
       </c>
     </row>
     <row r="62">
@@ -1223,13 +1223,13 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>0.1762679219245911</v>
+        <v>0.145416259765625</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0003929450467694551</v>
+        <v>0.00583156431093812</v>
       </c>
       <c r="D62" t="n">
-        <v>0.005813532508909702</v>
+        <v>0.7937121391296387</v>
       </c>
     </row>
     <row r="63">
@@ -1237,13 +1237,13 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>0.1752966791391373</v>
+        <v>0.1481899470090866</v>
       </c>
       <c r="C63" t="n">
-        <v>0.0003929485683329403</v>
+        <v>0.003679416375234723</v>
       </c>
       <c r="D63" t="n">
-        <v>0.006206878460943699</v>
+        <v>0.7166120409965515</v>
       </c>
     </row>
     <row r="64">
@@ -1251,13 +1251,13 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>0.1653101891279221</v>
+        <v>0.1353912651538849</v>
       </c>
       <c r="C64" t="n">
-        <v>0.0003929527010768652</v>
+        <v>0.003433716017752886</v>
       </c>
       <c r="D64" t="n">
-        <v>0.007470794953405857</v>
+        <v>0.7634785175323486</v>
       </c>
     </row>
     <row r="65">
@@ -1265,13 +1265,13 @@
         <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>0.1652324497699738</v>
+        <v>0.1417941153049469</v>
       </c>
       <c r="C65" t="n">
-        <v>0.0003929319209419191</v>
+        <v>0.003987383563071489</v>
       </c>
       <c r="D65" t="n">
-        <v>0.008088037371635437</v>
+        <v>0.7615258097648621</v>
       </c>
     </row>
     <row r="66">
@@ -1279,13 +1279,13 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>0.166137307882309</v>
+        <v>0.1428513079881668</v>
       </c>
       <c r="C66" t="n">
-        <v>0.0003929033409804106</v>
+        <v>0.004290429409593344</v>
       </c>
       <c r="D66" t="n">
-        <v>0.005199279170483351</v>
+        <v>0.7780566811561584</v>
       </c>
     </row>
     <row r="67">
@@ -1293,13 +1293,13 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>0.1659386456012726</v>
+        <v>0.1367515027523041</v>
       </c>
       <c r="C67" t="n">
-        <v>0.0003928687074221671</v>
+        <v>0.003562676487490535</v>
       </c>
       <c r="D67" t="n">
-        <v>0.005508871749043465</v>
+        <v>0.7464442849159241</v>
       </c>
     </row>
     <row r="68">
@@ -1307,13 +1307,13 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>0.1588084101676941</v>
+        <v>0.1508477628231049</v>
       </c>
       <c r="C68" t="n">
-        <v>0.0003928309306502342</v>
+        <v>0.004085735883563757</v>
       </c>
       <c r="D68" t="n">
-        <v>0.005346906371414661</v>
+        <v>0.7397358417510986</v>
       </c>
     </row>
     <row r="69">
@@ -1321,13 +1321,13 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>0.1532542854547501</v>
+        <v>0.1419197171926498</v>
       </c>
       <c r="C69" t="n">
-        <v>0.0003927808138541877</v>
+        <v>0.004288395401090384</v>
       </c>
       <c r="D69" t="n">
-        <v>0.004506886005401611</v>
+        <v>0.7463207244873047</v>
       </c>
     </row>
     <row r="70">
@@ -1335,13 +1335,13 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>0.1608017385005951</v>
+        <v>0.1392085999250412</v>
       </c>
       <c r="C70" t="n">
-        <v>0.000392708636354655</v>
+        <v>0.002977692987769842</v>
       </c>
       <c r="D70" t="n">
-        <v>0.003547218395397067</v>
+        <v>0.7618405222892761</v>
       </c>
     </row>
     <row r="71">
@@ -1349,13 +1349,13 @@
         <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>0.1643966883420944</v>
+        <v>0.1434624046087265</v>
       </c>
       <c r="C71" t="n">
-        <v>0.0003926728386431932</v>
+        <v>0.003263770136982203</v>
       </c>
       <c r="D71" t="n">
-        <v>0.006633618846535683</v>
+        <v>0.7572895288467407</v>
       </c>
     </row>
     <row r="72">
@@ -1363,13 +1363,13 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>0.1611075103282928</v>
+        <v>0.138542115688324</v>
       </c>
       <c r="C72" t="n">
-        <v>0.000392644782550633</v>
+        <v>0.00408483948558569</v>
       </c>
       <c r="D72" t="n">
-        <v>0.00470490287989378</v>
+        <v>0.7771466374397278</v>
       </c>
     </row>
     <row r="73">
@@ -1377,13 +1377,13 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>0.1590579152107239</v>
+        <v>0.1472816318273544</v>
       </c>
       <c r="C73" t="n">
-        <v>0.0003925979835912585</v>
+        <v>0.003415055805817246</v>
       </c>
       <c r="D73" t="n">
-        <v>0.004540023859590292</v>
+        <v>0.7585297822952271</v>
       </c>
     </row>
     <row r="74">
@@ -1391,13 +1391,13 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>0.153705433011055</v>
+        <v>0.152813509106636</v>
       </c>
       <c r="C74" t="n">
-        <v>0.0003925299388356507</v>
+        <v>0.006547901779413223</v>
       </c>
       <c r="D74" t="n">
-        <v>0.003305535763502121</v>
+        <v>0.7663182020187378</v>
       </c>
     </row>
     <row r="75">
@@ -1405,13 +1405,13 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>0.1507997661828995</v>
+        <v>0.1360475420951843</v>
       </c>
       <c r="C75" t="n">
-        <v>0.0003924639895558357</v>
+        <v>0.002836433006450534</v>
       </c>
       <c r="D75" t="n">
-        <v>0.003643307602033019</v>
+        <v>0.7092002034187317</v>
       </c>
     </row>
     <row r="76">
@@ -1419,13 +1419,13 @@
         <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>0.1616082936525345</v>
+        <v>0.1466005146503448</v>
       </c>
       <c r="C76" t="n">
-        <v>0.0003924065385945141</v>
+        <v>0.003678026609122753</v>
       </c>
       <c r="D76" t="n">
-        <v>0.004517938476055861</v>
+        <v>0.7396488189697266</v>
       </c>
     </row>
     <row r="77">
@@ -1433,13 +1433,13 @@
         <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>0.1598771959543228</v>
+        <v>0.1533324271440506</v>
       </c>
       <c r="C77" t="n">
-        <v>0.0003923665499314666</v>
+        <v>0.005646546836942434</v>
       </c>
       <c r="D77" t="n">
-        <v>0.0042823301628232</v>
+        <v>0.7204028964042664</v>
       </c>
     </row>
     <row r="78">
@@ -1447,13 +1447,13 @@
         <v>76</v>
       </c>
       <c r="B78" t="n">
-        <v>0.161076158285141</v>
+        <v>0.146181046962738</v>
       </c>
       <c r="C78" t="n">
-        <v>0.0003923237673006952</v>
+        <v>0.004736099857836962</v>
       </c>
       <c r="D78" t="n">
-        <v>0.005960450507700443</v>
+        <v>0.7662561535835266</v>
       </c>
     </row>
     <row r="79">
@@ -1461,13 +1461,13 @@
         <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>0.1606633365154266</v>
+        <v>0.1531694233417511</v>
       </c>
       <c r="C79" t="n">
-        <v>0.0003922697505913675</v>
+        <v>0.003105056472122669</v>
       </c>
       <c r="D79" t="n">
-        <v>0.00529361329972744</v>
+        <v>0.7445158958435059</v>
       </c>
     </row>
     <row r="80">
@@ -1475,13 +1475,13 @@
         <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>0.17172771692276</v>
+        <v>0.1322487741708755</v>
       </c>
       <c r="C80" t="n">
-        <v>0.0003921914612874389</v>
+        <v>0.003703431691974401</v>
       </c>
       <c r="D80" t="n">
-        <v>0.004847835283726454</v>
+        <v>0.740458607673645</v>
       </c>
     </row>
     <row r="81">
@@ -1489,13 +1489,13 @@
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>0.1703634262084961</v>
+        <v>0.1416146457195282</v>
       </c>
       <c r="C81" t="n">
-        <v>0.0003921723691746593</v>
+        <v>0.003699994646012783</v>
       </c>
       <c r="D81" t="n">
-        <v>0.007497589103877544</v>
+        <v>0.7235167026519775</v>
       </c>
     </row>
     <row r="82">
@@ -1503,13 +1503,13 @@
         <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>0.1715667843818665</v>
+        <v>0.1595657914876938</v>
       </c>
       <c r="C82" t="n">
-        <v>0.0003921647439710796</v>
+        <v>0.003963743802160025</v>
       </c>
       <c r="D82" t="n">
-        <v>0.005926533136516809</v>
+        <v>0.7289080619812012</v>
       </c>
     </row>
     <row r="83">
@@ -1517,13 +1517,13 @@
         <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>0.1560360193252563</v>
+        <v>0.1410400122404099</v>
       </c>
       <c r="C83" t="n">
-        <v>0.0003921546449419111</v>
+        <v>0.003654297906905413</v>
       </c>
       <c r="D83" t="n">
-        <v>0.00559332687407732</v>
+        <v>0.7416512370109558</v>
       </c>
     </row>
     <row r="84">
@@ -1531,13 +1531,13 @@
         <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>0.1614955961704254</v>
+        <v>0.1582292020320892</v>
       </c>
       <c r="C84" t="n">
-        <v>0.0003920882008969784</v>
+        <v>0.003850951790809631</v>
       </c>
       <c r="D84" t="n">
-        <v>0.004808841273188591</v>
+        <v>0.7227863073348999</v>
       </c>
     </row>
     <row r="85">
@@ -1545,13 +1545,13 @@
         <v>83</v>
       </c>
       <c r="B85" t="n">
-        <v>0.1604605317115784</v>
+        <v>0.1566924303770065</v>
       </c>
       <c r="C85" t="n">
-        <v>0.0003920331946574152</v>
+        <v>0.003858908545225859</v>
       </c>
       <c r="D85" t="n">
-        <v>0.006666325964033604</v>
+        <v>0.7096385955810547</v>
       </c>
     </row>
     <row r="86">
@@ -1559,13 +1559,13 @@
         <v>84</v>
       </c>
       <c r="B86" t="n">
-        <v>0.1674911826848984</v>
+        <v>0.1382725089788437</v>
       </c>
       <c r="C86" t="n">
-        <v>0.0003919769660569727</v>
+        <v>0.004448487889021635</v>
       </c>
       <c r="D86" t="n">
-        <v>0.006056053563952446</v>
+        <v>0.7835190296173096</v>
       </c>
     </row>
     <row r="87">
@@ -1573,13 +1573,13 @@
         <v>85</v>
       </c>
       <c r="B87" t="n">
-        <v>0.1714696437120438</v>
+        <v>0.1458203941583633</v>
       </c>
       <c r="C87" t="n">
-        <v>0.0003919632290489972</v>
+        <v>0.003541660029441118</v>
       </c>
       <c r="D87" t="n">
-        <v>0.006435533054172993</v>
+        <v>0.719363272190094</v>
       </c>
     </row>
     <row r="88">
@@ -1587,13 +1587,13 @@
         <v>86</v>
       </c>
       <c r="B88" t="n">
-        <v>0.1697093546390533</v>
+        <v>0.150025486946106</v>
       </c>
       <c r="C88" t="n">
-        <v>0.0003919642767868936</v>
+        <v>0.004276533611118793</v>
       </c>
       <c r="D88" t="n">
-        <v>0.007444675080478191</v>
+        <v>0.7042069435119629</v>
       </c>
     </row>
     <row r="89">
@@ -1601,13 +1601,13 @@
         <v>87</v>
       </c>
       <c r="B89" t="n">
-        <v>0.1642940640449524</v>
+        <v>0.1444728821516037</v>
       </c>
       <c r="C89" t="n">
-        <v>0.0003919503069482744</v>
+        <v>0.003851034212857485</v>
       </c>
       <c r="D89" t="n">
-        <v>0.005462308414280415</v>
+        <v>0.7436504364013672</v>
       </c>
     </row>
     <row r="90">
@@ -1615,13 +1615,13 @@
         <v>88</v>
       </c>
       <c r="B90" t="n">
-        <v>0.1592437326908112</v>
+        <v>0.1513262391090393</v>
       </c>
       <c r="C90" t="n">
-        <v>0.000391916953958571</v>
+        <v>0.003927387297153473</v>
       </c>
       <c r="D90" t="n">
-        <v>0.005960158072412014</v>
+        <v>0.7265955805778503</v>
       </c>
     </row>
     <row r="91">
@@ -1629,13 +1629,13 @@
         <v>89</v>
       </c>
       <c r="B91" t="n">
-        <v>0.1661011278629303</v>
+        <v>0.1501328498125076</v>
       </c>
       <c r="C91" t="n">
-        <v>0.0003918702132068574</v>
+        <v>0.004097898956388235</v>
       </c>
       <c r="D91" t="n">
-        <v>0.005347957834601402</v>
+        <v>0.7807452082633972</v>
       </c>
     </row>
     <row r="92">
@@ -1643,13 +1643,13 @@
         <v>90</v>
       </c>
       <c r="B92" t="n">
-        <v>0.1652845144271851</v>
+        <v>0.1433850526809692</v>
       </c>
       <c r="C92" t="n">
-        <v>0.0003918497241102159</v>
+        <v>0.003747861133888364</v>
       </c>
       <c r="D92" t="n">
-        <v>0.004710651934146881</v>
+        <v>0.7047158479690552</v>
       </c>
     </row>
     <row r="93">
@@ -1657,13 +1657,13 @@
         <v>91</v>
       </c>
       <c r="B93" t="n">
-        <v>0.1577392071485519</v>
+        <v>0.1373685151338577</v>
       </c>
       <c r="C93" t="n">
-        <v>0.0003918339498341084</v>
+        <v>0.003389672841876745</v>
       </c>
       <c r="D93" t="n">
-        <v>0.004907595925033092</v>
+        <v>0.7413076162338257</v>
       </c>
     </row>
     <row r="94">
@@ -1671,13 +1671,13 @@
         <v>92</v>
       </c>
       <c r="B94" t="n">
-        <v>0.1540071815252304</v>
+        <v>0.1470435261726379</v>
       </c>
       <c r="C94" t="n">
-        <v>0.0003917876747436821</v>
+        <v>0.002984044840559363</v>
       </c>
       <c r="D94" t="n">
-        <v>0.004860761575400829</v>
+        <v>0.7527149319648743</v>
       </c>
     </row>
     <row r="95">
@@ -1685,13 +1685,13 @@
         <v>93</v>
       </c>
       <c r="B95" t="n">
-        <v>0.1724509298801422</v>
+        <v>0.1417749226093292</v>
       </c>
       <c r="C95" t="n">
-        <v>0.0003917512949556112</v>
+        <v>0.003689714940264821</v>
       </c>
       <c r="D95" t="n">
-        <v>0.004671864211559296</v>
+        <v>0.73867267370224</v>
       </c>
     </row>
     <row r="96">
@@ -1699,13 +1699,13 @@
         <v>94</v>
       </c>
       <c r="B96" t="n">
-        <v>0.1720687747001648</v>
+        <v>0.1459866315126419</v>
       </c>
       <c r="C96" t="n">
-        <v>0.0003917478024959564</v>
+        <v>0.005330318119376898</v>
       </c>
       <c r="D96" t="n">
-        <v>0.004433623980730772</v>
+        <v>0.7240041494369507</v>
       </c>
     </row>
     <row r="97">
@@ -1713,13 +1713,13 @@
         <v>95</v>
       </c>
       <c r="B97" t="n">
-        <v>0.1663038432598114</v>
+        <v>0.1543257236480713</v>
       </c>
       <c r="C97" t="n">
-        <v>0.0003917249850928783</v>
+        <v>0.005020190495997667</v>
       </c>
       <c r="D97" t="n">
-        <v>0.004696169402450323</v>
+        <v>0.7272516489028931</v>
       </c>
     </row>
     <row r="98">
@@ -1727,13 +1727,13 @@
         <v>96</v>
       </c>
       <c r="B98" t="n">
-        <v>0.1724341213703156</v>
+        <v>0.1498250365257263</v>
       </c>
       <c r="C98" t="n">
-        <v>0.0003917101421393454</v>
+        <v>0.005412811413407326</v>
       </c>
       <c r="D98" t="n">
-        <v>0.004908005706965923</v>
+        <v>0.6952725052833557</v>
       </c>
     </row>
     <row r="99">
@@ -1741,13 +1741,13 @@
         <v>97</v>
       </c>
       <c r="B99" t="n">
-        <v>0.1698392033576965</v>
+        <v>0.1434644162654877</v>
       </c>
       <c r="C99" t="n">
-        <v>0.0003917038266081363</v>
+        <v>0.003912460058927536</v>
       </c>
       <c r="D99" t="n">
-        <v>0.004568429198116064</v>
+        <v>0.7368627786636353</v>
       </c>
     </row>
     <row r="100">
@@ -1755,13 +1755,13 @@
         <v>98</v>
       </c>
       <c r="B100" t="n">
-        <v>0.1695348173379898</v>
+        <v>0.1548875570297241</v>
       </c>
       <c r="C100" t="n">
-        <v>0.0003916872956324369</v>
+        <v>0.006684909574687481</v>
       </c>
       <c r="D100" t="n">
-        <v>0.003883983939886093</v>
+        <v>0.7171368002891541</v>
       </c>
     </row>
     <row r="101">
@@ -1769,13 +1769,13 @@
         <v>99</v>
       </c>
       <c r="B101" t="n">
-        <v>0.1644922345876694</v>
+        <v>0.1522788256406784</v>
       </c>
       <c r="C101" t="n">
-        <v>0.0003916675341315567</v>
+        <v>0.00601063622161746</v>
       </c>
       <c r="D101" t="n">
-        <v>0.005509225185960531</v>
+        <v>0.7276734709739685</v>
       </c>
     </row>
   </sheetData>
